--- a/upload/employee.xlsx
+++ b/upload/employee.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="576">
   <si>
     <t>Subsidiary</t>
   </si>
@@ -1739,7 +1739,10 @@
     <t>Duplicated</t>
   </si>
   <si>
-    <t>2024-02-18 16:47:05</t>
+    <t>2024-02-25 16:16:20</t>
+  </si>
+  <si>
+    <t>2024-02-25 16:16:21</t>
   </si>
 </sst>
 </file>
@@ -5035,7 +5038,7 @@
         <v>573</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5055,7 +5058,7 @@
         <v>573</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -5075,7 +5078,7 @@
         <v>573</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -5095,7 +5098,7 @@
         <v>573</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5115,7 +5118,7 @@
         <v>573</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -5135,7 +5138,7 @@
         <v>573</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -5155,7 +5158,7 @@
         <v>573</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5175,7 +5178,7 @@
         <v>573</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5195,7 +5198,7 @@
         <v>573</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5215,7 +5218,7 @@
         <v>573</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -5235,7 +5238,7 @@
         <v>573</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -5255,7 +5258,7 @@
         <v>573</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -5275,7 +5278,7 @@
         <v>573</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -5295,7 +5298,7 @@
         <v>573</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -5315,7 +5318,7 @@
         <v>573</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -5335,7 +5338,7 @@
         <v>573</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -5355,7 +5358,7 @@
         <v>573</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5375,7 +5378,7 @@
         <v>573</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -5395,7 +5398,7 @@
         <v>573</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5415,7 +5418,7 @@
         <v>573</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5435,7 +5438,7 @@
         <v>573</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5455,7 +5458,7 @@
         <v>573</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5475,7 +5478,7 @@
         <v>573</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5495,7 +5498,7 @@
         <v>573</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -5515,7 +5518,7 @@
         <v>573</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5535,7 +5538,7 @@
         <v>573</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -5555,7 +5558,7 @@
         <v>573</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5575,7 +5578,7 @@
         <v>573</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -5595,7 +5598,7 @@
         <v>573</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5615,7 +5618,7 @@
         <v>573</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -5635,7 +5638,7 @@
         <v>573</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5655,7 +5658,7 @@
         <v>573</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -5675,7 +5678,7 @@
         <v>573</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5695,7 +5698,7 @@
         <v>573</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -5715,7 +5718,7 @@
         <v>573</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5735,7 +5738,7 @@
         <v>573</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5755,7 +5758,7 @@
         <v>573</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5775,7 +5778,7 @@
         <v>573</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -5795,7 +5798,7 @@
         <v>573</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5815,7 +5818,7 @@
         <v>573</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -5835,7 +5838,7 @@
         <v>573</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -5855,7 +5858,7 @@
         <v>573</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -5875,7 +5878,7 @@
         <v>573</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -5895,7 +5898,7 @@
         <v>573</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -5915,7 +5918,7 @@
         <v>573</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -5935,7 +5938,7 @@
         <v>573</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -5955,7 +5958,7 @@
         <v>573</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -5975,7 +5978,7 @@
         <v>573</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -5995,7 +5998,7 @@
         <v>573</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -6015,7 +6018,7 @@
         <v>573</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -6035,7 +6038,7 @@
         <v>573</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -6055,7 +6058,7 @@
         <v>573</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -6075,7 +6078,7 @@
         <v>573</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -6095,7 +6098,7 @@
         <v>573</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -6115,7 +6118,7 @@
         <v>573</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -6135,7 +6138,7 @@
         <v>573</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -6155,7 +6158,7 @@
         <v>573</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -6175,7 +6178,7 @@
         <v>573</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -6195,7 +6198,7 @@
         <v>573</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -6215,7 +6218,7 @@
         <v>573</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -6235,7 +6238,7 @@
         <v>573</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -6255,7 +6258,7 @@
         <v>573</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -6275,7 +6278,7 @@
         <v>573</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -6295,7 +6298,7 @@
         <v>573</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -6315,7 +6318,7 @@
         <v>573</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -6335,7 +6338,7 @@
         <v>573</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -6355,7 +6358,7 @@
         <v>573</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -6375,7 +6378,7 @@
         <v>573</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -6395,7 +6398,7 @@
         <v>573</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -6415,7 +6418,7 @@
         <v>573</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -6435,7 +6438,7 @@
         <v>573</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -6455,7 +6458,7 @@
         <v>573</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -6475,7 +6478,7 @@
         <v>573</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -6495,7 +6498,7 @@
         <v>573</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -6515,7 +6518,7 @@
         <v>573</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -6535,7 +6538,7 @@
         <v>573</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -6555,7 +6558,7 @@
         <v>573</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -6575,7 +6578,7 @@
         <v>573</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -6595,7 +6598,7 @@
         <v>573</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -6615,7 +6618,7 @@
         <v>573</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -6635,7 +6638,7 @@
         <v>573</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -6655,7 +6658,7 @@
         <v>573</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -6675,7 +6678,7 @@
         <v>573</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -6695,7 +6698,7 @@
         <v>573</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -6715,7 +6718,7 @@
         <v>573</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -6735,7 +6738,7 @@
         <v>573</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -6755,7 +6758,7 @@
         <v>573</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -6775,7 +6778,7 @@
         <v>573</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -6795,7 +6798,7 @@
         <v>573</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -6815,7 +6818,7 @@
         <v>573</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -6835,7 +6838,7 @@
         <v>573</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -6855,7 +6858,7 @@
         <v>573</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -6875,7 +6878,7 @@
         <v>573</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -6895,7 +6898,7 @@
         <v>573</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -6915,7 +6918,7 @@
         <v>573</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -6935,7 +6938,7 @@
         <v>573</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -6955,7 +6958,7 @@
         <v>573</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -6975,7 +6978,7 @@
         <v>573</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -6995,7 +6998,7 @@
         <v>573</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -7015,7 +7018,7 @@
         <v>573</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -7035,7 +7038,7 @@
         <v>573</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -7055,7 +7058,7 @@
         <v>573</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -7075,7 +7078,7 @@
         <v>573</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -7095,7 +7098,7 @@
         <v>573</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -7115,7 +7118,7 @@
         <v>573</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -7135,7 +7138,7 @@
         <v>573</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -7155,7 +7158,7 @@
         <v>573</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -7175,7 +7178,7 @@
         <v>573</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -7195,7 +7198,7 @@
         <v>573</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -7215,7 +7218,7 @@
         <v>573</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -7235,7 +7238,7 @@
         <v>573</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -7255,7 +7258,7 @@
         <v>573</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -7275,7 +7278,7 @@
         <v>573</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -7295,7 +7298,7 @@
         <v>573</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -7315,7 +7318,7 @@
         <v>573</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -7335,7 +7338,7 @@
         <v>573</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
